--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="2"/>
+    <workbookView windowHeight="17680" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -18587,7 +18587,7 @@
         <v>10</v>
       </c>
       <c r="E9" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>373</v>
@@ -18633,7 +18633,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>376</v>
@@ -18679,7 +18679,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>379</v>
@@ -18723,7 +18723,8 @@
         <v>10</v>
       </c>
       <c r="E12" s="2">
-        <v>30</v>
+        <f t="shared" ref="E12:E41" si="0">E9+5</f>
+        <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>380</v>
@@ -18769,7 +18770,8 @@
         <v>10</v>
       </c>
       <c r="E13" s="2">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>383</v>
@@ -18813,7 +18815,8 @@
         <v>10</v>
       </c>
       <c r="E14" s="2">
-        <v>30</v>
+        <f t="shared" si="0"/>
+        <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>385</v>
@@ -18857,7 +18860,8 @@
         <v>10</v>
       </c>
       <c r="E15" s="2">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>386</v>
@@ -18903,7 +18907,8 @@
         <v>10</v>
       </c>
       <c r="E16" s="2">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>389</v>
@@ -18947,7 +18952,8 @@
         <v>10</v>
       </c>
       <c r="E17" s="2">
-        <v>40</v>
+        <f t="shared" si="0"/>
+        <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>390</v>
@@ -18991,7 +18997,8 @@
         <v>10</v>
       </c>
       <c r="E18" s="2">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>392</v>
@@ -19037,7 +19044,8 @@
         <v>10</v>
       </c>
       <c r="E19" s="2">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>395</v>
@@ -19081,7 +19089,8 @@
         <v>10</v>
       </c>
       <c r="E20" s="2">
-        <v>50</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>397</v>
@@ -19125,7 +19134,8 @@
         <v>10</v>
       </c>
       <c r="E21" s="2">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>398</v>
@@ -19171,7 +19181,8 @@
         <v>10</v>
       </c>
       <c r="E22" s="2">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>401</v>
@@ -19215,7 +19226,8 @@
         <v>10</v>
       </c>
       <c r="E23" s="2">
-        <v>60</v>
+        <f t="shared" si="0"/>
+        <v>35</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>403</v>
@@ -19258,7 +19270,8 @@
         <v>10</v>
       </c>
       <c r="E24" s="2">
-        <v>70</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>404</v>
@@ -19303,7 +19316,8 @@
         <v>10</v>
       </c>
       <c r="E25" s="2">
-        <v>70</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>407</v>
@@ -19346,7 +19360,8 @@
         <v>10</v>
       </c>
       <c r="E26" s="2">
-        <v>70</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>409</v>
@@ -19390,7 +19405,8 @@
         <v>10</v>
       </c>
       <c r="E27" s="2">
-        <v>80</v>
+        <f t="shared" si="0"/>
+        <v>45</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>410</v>
@@ -19436,7 +19452,8 @@
         <v>10</v>
       </c>
       <c r="E28" s="2">
-        <v>80</v>
+        <f t="shared" si="0"/>
+        <v>45</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>413</v>
@@ -19480,7 +19497,8 @@
         <v>10</v>
       </c>
       <c r="E29" s="2">
-        <v>80</v>
+        <f t="shared" si="0"/>
+        <v>45</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>415</v>
@@ -19524,7 +19542,8 @@
         <v>10</v>
       </c>
       <c r="E30" s="2">
-        <v>90</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>416</v>
@@ -19570,7 +19589,8 @@
         <v>10</v>
       </c>
       <c r="E31" s="2">
-        <v>90</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>419</v>
@@ -19614,7 +19634,8 @@
         <v>10</v>
       </c>
       <c r="E32" s="2">
-        <v>90</v>
+        <f t="shared" si="0"/>
+        <v>50</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>421</v>
@@ -19658,7 +19679,8 @@
         <v>10</v>
       </c>
       <c r="E33" s="2">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>55</v>
       </c>
       <c r="F33" s="2" t="s">
         <v>422</v>
@@ -19704,7 +19726,8 @@
         <v>10</v>
       </c>
       <c r="E34" s="2">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>55</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>425</v>
@@ -19748,7 +19771,8 @@
         <v>10</v>
       </c>
       <c r="E35" s="2">
-        <v>100</v>
+        <f t="shared" si="0"/>
+        <v>55</v>
       </c>
       <c r="F35" s="2" t="s">
         <v>427</v>
@@ -19789,8 +19813,9 @@
       <c r="D36" s="2">
         <v>10</v>
       </c>
-      <c r="E36" s="1">
-        <v>110</v>
+      <c r="E36" s="2">
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>428</v>
@@ -19831,8 +19856,9 @@
       <c r="D37" s="2">
         <v>10</v>
       </c>
-      <c r="E37" s="1">
-        <v>110</v>
+      <c r="E37" s="2">
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>430</v>
@@ -19875,8 +19901,9 @@
       <c r="D38" s="2">
         <v>10</v>
       </c>
-      <c r="E38" s="1">
-        <v>110</v>
+      <c r="E38" s="2">
+        <f t="shared" si="0"/>
+        <v>60</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>432</v>
@@ -19919,8 +19946,9 @@
       <c r="D39" s="2">
         <v>10</v>
       </c>
-      <c r="E39" s="1">
-        <v>120</v>
+      <c r="E39" s="2">
+        <f t="shared" si="0"/>
+        <v>65</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>433</v>
@@ -19963,8 +19991,9 @@
       <c r="D40" s="2">
         <v>10</v>
       </c>
-      <c r="E40" s="1">
-        <v>120</v>
+      <c r="E40" s="2">
+        <f t="shared" si="0"/>
+        <v>65</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>435</v>
@@ -20007,8 +20036,9 @@
       <c r="D41" s="2">
         <v>10</v>
       </c>
-      <c r="E41" s="1">
-        <v>120</v>
+      <c r="E41" s="2">
+        <f t="shared" si="0"/>
+        <v>65</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>437</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,14 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="4"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
     <sheet name="50-80" sheetId="8" r:id="rId2"/>
     <sheet name="90-120" sheetId="9" r:id="rId3"/>
-    <sheet name="定制" sheetId="10" r:id="rId4"/>
-    <sheet name="传奇装备" sheetId="11" r:id="rId5"/>
+    <sheet name="新版" sheetId="12" r:id="rId4"/>
+    <sheet name="定制" sheetId="10" r:id="rId5"/>
+    <sheet name="传奇装备" sheetId="11" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -355,8 +356,72 @@
 </comments>
 </file>
 
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>admin</author>
+  </authors>
+  <commentList>
+    <comment ref="H3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 武器
+2 衣服
+3 头盔
+4 项链
+5 左手镯
+6 右手镯
+7 左戒指
+8 右戒指
+9 腰带
+10 鞋子
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+属性ID列表</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1320" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="472">
   <si>
     <t>_id</t>
   </si>
@@ -1418,6 +1483,84 @@
   </si>
   <si>
     <t>暗龙道靴</t>
+  </si>
+  <si>
+    <t>天龙战刃</t>
+  </si>
+  <si>
+    <t>60000,40</t>
+  </si>
+  <si>
+    <t>天龙战甲</t>
+  </si>
+  <si>
+    <t>天龙战链</t>
+  </si>
+  <si>
+    <t>30000,20</t>
+  </si>
+  <si>
+    <t>天龙战盔</t>
+  </si>
+  <si>
+    <t>天龙战镯</t>
+  </si>
+  <si>
+    <t>天龙战戒</t>
+  </si>
+  <si>
+    <t>天龙战带</t>
+  </si>
+  <si>
+    <t>天龙战靴</t>
+  </si>
+  <si>
+    <t>天龙法杖</t>
+  </si>
+  <si>
+    <t>天龙法衣</t>
+  </si>
+  <si>
+    <t>天龙法链</t>
+  </si>
+  <si>
+    <t>天龙法盔</t>
+  </si>
+  <si>
+    <t>天龙法镯</t>
+  </si>
+  <si>
+    <t>天龙法戒</t>
+  </si>
+  <si>
+    <t>天龙法带</t>
+  </si>
+  <si>
+    <t>天龙法靴</t>
+  </si>
+  <si>
+    <t>天龙道剑</t>
+  </si>
+  <si>
+    <t>天龙道袍</t>
+  </si>
+  <si>
+    <t>天龙道链</t>
+  </si>
+  <si>
+    <t>天龙道盔</t>
+  </si>
+  <si>
+    <t>天龙道镯</t>
+  </si>
+  <si>
+    <t>天龙道戒</t>
+  </si>
+  <si>
+    <t>天龙道带</t>
+  </si>
+  <si>
+    <t>天龙道靴</t>
   </si>
   <si>
     <t>新手武器</t>
@@ -17989,6 +18132,1306 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
+  <dimension ref="A1:Q29"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
+  <cols>
+    <col min="5" max="5" width="14.1666666666667" customWidth="1"/>
+    <col min="8" max="8" width="10.1666666666667" customWidth="1"/>
+    <col min="9" max="9" width="11.3333333333333" customWidth="1"/>
+    <col min="10" max="10" width="12.75" customWidth="1"/>
+    <col min="13" max="13" width="12.5833333333333" customWidth="1"/>
+    <col min="14" max="14" width="12.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" ht="18" customHeight="1"/>
+    <row r="2" s="1" customFormat="1" ht="18" customHeight="1"/>
+    <row r="3" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="A3" s="9"/>
+      <c r="C3" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="A4" s="9"/>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="M4" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="P4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q4" s="7" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="A5" s="9"/>
+      <c r="C5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="O5" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="P5" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C6" s="1">
+        <v>240001</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1">
+        <v>61</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
+      </c>
+      <c r="I6" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K6" s="9">
+        <v>4500</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1">
+        <v>37</v>
+      </c>
+      <c r="O6" s="1">
+        <v>5</v>
+      </c>
+      <c r="P6" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C7" s="1">
+        <v>240002</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
+      <c r="E7" s="1">
+        <v>61</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="G7" s="1">
+        <v>2</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K7" s="9">
+        <v>4500</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1">
+        <v>38</v>
+      </c>
+      <c r="O7" s="1">
+        <v>5</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C8" s="1">
+        <v>240003</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
+      <c r="E8" s="1">
+        <v>61</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="G8" s="1">
+        <v>3</v>
+      </c>
+      <c r="H8" s="1">
+        <v>3</v>
+      </c>
+      <c r="I8" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K8" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1">
+        <v>39</v>
+      </c>
+      <c r="O8" s="1">
+        <v>5</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C9" s="1">
+        <v>240004</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1">
+        <v>61</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="G9" s="1">
+        <v>4</v>
+      </c>
+      <c r="H9" s="1">
+        <v>4</v>
+      </c>
+      <c r="I9" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K9" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1">
+        <v>39</v>
+      </c>
+      <c r="O9" s="1">
+        <v>5</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C10" s="1">
+        <v>240005</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1">
+        <v>61</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G10" s="1">
+        <v>5</v>
+      </c>
+      <c r="H10" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K10" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1">
+        <v>39</v>
+      </c>
+      <c r="O10" s="1">
+        <v>5</v>
+      </c>
+      <c r="P10" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C11" s="1">
+        <v>240006</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1">
+        <v>61</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="G11" s="1">
+        <v>7</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K11" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1">
+        <v>39</v>
+      </c>
+      <c r="O11" s="1">
+        <v>5</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C12" s="1">
+        <v>240007</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1">
+        <v>61</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="G12" s="1">
+        <v>9</v>
+      </c>
+      <c r="H12" s="1">
+        <v>9</v>
+      </c>
+      <c r="I12" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K12" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1">
+        <v>39</v>
+      </c>
+      <c r="O12" s="1">
+        <v>5</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C13" s="1">
+        <v>240008</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1">
+        <v>61</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="G13" s="1">
+        <v>10</v>
+      </c>
+      <c r="H13" s="1">
+        <v>10</v>
+      </c>
+      <c r="I13" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K13" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1">
+        <v>39</v>
+      </c>
+      <c r="O13" s="1">
+        <v>5</v>
+      </c>
+      <c r="P13" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C14" s="1">
+        <v>250001</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
+      <c r="E14" s="1">
+        <v>61</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>1</v>
+      </c>
+      <c r="I14" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K14" s="9">
+        <v>4500</v>
+      </c>
+      <c r="L14" s="1">
+        <v>2</v>
+      </c>
+      <c r="M14" s="1">
+        <v>0</v>
+      </c>
+      <c r="N14" s="1">
+        <v>37</v>
+      </c>
+      <c r="O14" s="1">
+        <v>5</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C15" s="1">
+        <v>250002</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>61</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G15" s="1">
+        <v>2</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2</v>
+      </c>
+      <c r="I15" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K15" s="9">
+        <v>4500</v>
+      </c>
+      <c r="L15" s="1">
+        <v>2</v>
+      </c>
+      <c r="M15" s="1">
+        <v>0</v>
+      </c>
+      <c r="N15" s="1">
+        <v>38</v>
+      </c>
+      <c r="O15" s="1">
+        <v>5</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="1" ht="18" customHeight="1" spans="1:17">
+      <c r="C16" s="1">
+        <v>250003</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>61</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G16" s="1">
+        <v>3</v>
+      </c>
+      <c r="H16" s="1">
+        <v>3</v>
+      </c>
+      <c r="I16" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="J16" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K16" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L16" s="1">
+        <v>2</v>
+      </c>
+      <c r="M16" s="1">
+        <v>0</v>
+      </c>
+      <c r="N16" s="1">
+        <v>39</v>
+      </c>
+      <c r="O16" s="1">
+        <v>5</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C17" s="1">
+        <v>250004</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>61</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="G17" s="1">
+        <v>4</v>
+      </c>
+      <c r="H17" s="1">
+        <v>4</v>
+      </c>
+      <c r="I17" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J17" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K17" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L17" s="1">
+        <v>2</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>39</v>
+      </c>
+      <c r="O17" s="1">
+        <v>5</v>
+      </c>
+      <c r="P17" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C18" s="1">
+        <v>250005</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="1">
+        <v>61</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I18" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K18" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L18" s="1">
+        <v>2</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>39</v>
+      </c>
+      <c r="O18" s="1">
+        <v>5</v>
+      </c>
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C19" s="1">
+        <v>250006</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
+      <c r="E19" s="1">
+        <v>61</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="G19" s="1">
+        <v>7</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I19" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K19" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L19" s="1">
+        <v>2</v>
+      </c>
+      <c r="M19" s="1">
+        <v>0</v>
+      </c>
+      <c r="N19" s="1">
+        <v>39</v>
+      </c>
+      <c r="O19" s="1">
+        <v>5</v>
+      </c>
+      <c r="P19" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C20" s="1">
+        <v>250007</v>
+      </c>
+      <c r="D20" s="1">
+        <v>1</v>
+      </c>
+      <c r="E20" s="1">
+        <v>61</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="G20" s="1">
+        <v>9</v>
+      </c>
+      <c r="H20" s="1">
+        <v>9</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J20" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K20" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L20" s="1">
+        <v>2</v>
+      </c>
+      <c r="M20" s="1">
+        <v>0</v>
+      </c>
+      <c r="N20" s="1">
+        <v>39</v>
+      </c>
+      <c r="O20" s="1">
+        <v>5</v>
+      </c>
+      <c r="P20" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C21" s="1">
+        <v>250008</v>
+      </c>
+      <c r="D21" s="1">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1">
+        <v>61</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="G21" s="1">
+        <v>10</v>
+      </c>
+      <c r="H21" s="1">
+        <v>10</v>
+      </c>
+      <c r="I21" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K21" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L21" s="1">
+        <v>2</v>
+      </c>
+      <c r="M21" s="1">
+        <v>0</v>
+      </c>
+      <c r="N21" s="1">
+        <v>39</v>
+      </c>
+      <c r="O21" s="1">
+        <v>5</v>
+      </c>
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C22" s="1">
+        <v>260001</v>
+      </c>
+      <c r="D22" s="1">
+        <v>1</v>
+      </c>
+      <c r="E22" s="1">
+        <v>61</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="G22" s="1">
+        <v>1</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
+      <c r="I22" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K22" s="9">
+        <v>4500</v>
+      </c>
+      <c r="L22" s="1">
+        <v>3</v>
+      </c>
+      <c r="M22" s="1">
+        <v>0</v>
+      </c>
+      <c r="N22" s="1">
+        <v>37</v>
+      </c>
+      <c r="O22" s="1">
+        <v>5</v>
+      </c>
+      <c r="P22" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C23" s="1">
+        <v>260002</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="1">
+        <v>61</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="G23" s="1">
+        <v>2</v>
+      </c>
+      <c r="H23" s="1">
+        <v>2</v>
+      </c>
+      <c r="I23" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K23" s="9">
+        <v>4500</v>
+      </c>
+      <c r="L23" s="1">
+        <v>3</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>38</v>
+      </c>
+      <c r="O23" s="1">
+        <v>5</v>
+      </c>
+      <c r="P23" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C24" s="1">
+        <v>260003</v>
+      </c>
+      <c r="D24" s="1">
+        <v>1</v>
+      </c>
+      <c r="E24" s="1">
+        <v>61</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G24" s="1">
+        <v>3</v>
+      </c>
+      <c r="H24" s="1">
+        <v>3</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J24" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K24" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L24" s="1">
+        <v>3</v>
+      </c>
+      <c r="M24" s="1">
+        <v>0</v>
+      </c>
+      <c r="N24" s="1">
+        <v>39</v>
+      </c>
+      <c r="O24" s="1">
+        <v>5</v>
+      </c>
+      <c r="P24" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C25" s="1">
+        <v>260004</v>
+      </c>
+      <c r="D25" s="1">
+        <v>1</v>
+      </c>
+      <c r="E25" s="1">
+        <v>61</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G25" s="1">
+        <v>4</v>
+      </c>
+      <c r="H25" s="1">
+        <v>4</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K25" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L25" s="1">
+        <v>3</v>
+      </c>
+      <c r="M25" s="1">
+        <v>0</v>
+      </c>
+      <c r="N25" s="1">
+        <v>39</v>
+      </c>
+      <c r="O25" s="1">
+        <v>5</v>
+      </c>
+      <c r="P25" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C26" s="1">
+        <v>260005</v>
+      </c>
+      <c r="D26" s="1">
+        <v>1</v>
+      </c>
+      <c r="E26" s="1">
+        <v>61</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K26" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L26" s="1">
+        <v>3</v>
+      </c>
+      <c r="M26" s="1">
+        <v>0</v>
+      </c>
+      <c r="N26" s="1">
+        <v>39</v>
+      </c>
+      <c r="O26" s="1">
+        <v>5</v>
+      </c>
+      <c r="P26" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C27" s="1">
+        <v>260006</v>
+      </c>
+      <c r="D27" s="1">
+        <v>1</v>
+      </c>
+      <c r="E27" s="1">
+        <v>61</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="G27" s="1">
+        <v>7</v>
+      </c>
+      <c r="H27" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="J27" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K27" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L27" s="1">
+        <v>3</v>
+      </c>
+      <c r="M27" s="1">
+        <v>0</v>
+      </c>
+      <c r="N27" s="1">
+        <v>39</v>
+      </c>
+      <c r="O27" s="1">
+        <v>5</v>
+      </c>
+      <c r="P27" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C28" s="1">
+        <v>260007</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="1">
+        <v>61</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="G28" s="1">
+        <v>9</v>
+      </c>
+      <c r="H28" s="1">
+        <v>9</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J28" s="17" t="s">
+        <v>358</v>
+      </c>
+      <c r="K28" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L28" s="1">
+        <v>3</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>39</v>
+      </c>
+      <c r="O28" s="1">
+        <v>5</v>
+      </c>
+      <c r="P28" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" customFormat="1" ht="18" customHeight="1" spans="3:17">
+      <c r="C29" s="1">
+        <v>260008</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="1">
+        <v>61</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="G29" s="1">
+        <v>10</v>
+      </c>
+      <c r="H29" s="1">
+        <v>10</v>
+      </c>
+      <c r="I29" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="17" t="s">
+        <v>355</v>
+      </c>
+      <c r="K29" s="9">
+        <v>1500</v>
+      </c>
+      <c r="L29" s="1">
+        <v>3</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>39</v>
+      </c>
+      <c r="O29" s="1">
+        <v>5</v>
+      </c>
+      <c r="P29" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:H5 K3:Q5" errorStyle="warning">
+      <formula1>COUNTIF($A:$A,C3)&lt;2</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q7"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14" outlineLevelRow="6"/>
   <cols>
@@ -18155,7 +19598,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>354</v>
+        <v>380</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -18164,10 +19607,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>355</v>
+        <v>381</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>356</v>
+        <v>382</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -18202,7 +19645,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>357</v>
+        <v>383</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -18211,10 +19654,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>358</v>
+        <v>384</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>359</v>
+        <v>385</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -18250,7 +19693,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:P78"/>
@@ -18286,7 +19729,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18304,7 +19747,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -18335,16 +19778,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>361</v>
+        <v>387</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -18381,10 +19824,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>364</v>
+        <v>390</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>362</v>
+        <v>388</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -18454,7 +19897,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>365</v>
+        <v>391</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -18466,7 +19909,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>366</v>
+        <v>392</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -18478,7 +19921,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>367</v>
+        <v>393</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -18500,7 +19943,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>368</v>
+        <v>394</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -18509,10 +19952,10 @@
         <v>34</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -18524,7 +19967,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>371</v>
+        <v>397</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -18546,7 +19989,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -18558,7 +20001,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>370</v>
+        <v>396</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -18590,7 +20033,7 @@
         <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -18602,7 +20045,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -18614,7 +20057,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -18636,7 +20079,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -18645,10 +20088,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -18660,7 +20103,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -18682,7 +20125,7 @@
         <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -18694,7 +20137,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -18727,7 +20170,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -18736,10 +20179,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -18751,7 +20194,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -18774,7 +20217,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -18786,7 +20229,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -18819,7 +20262,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -18831,7 +20274,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -18864,7 +20307,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="G15" s="1">
         <v>4</v>
@@ -18873,10 +20316,10 @@
         <v>4</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="K15" s="2">
         <v>10</v>
@@ -18888,7 +20331,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -18911,7 +20354,7 @@
         <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -18923,7 +20366,7 @@
         <v>27</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="K16" s="2">
         <v>11</v>
@@ -18956,7 +20399,7 @@
         <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="G17" s="1">
         <v>7</v>
@@ -18968,7 +20411,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="K17" s="2">
         <v>12</v>
@@ -19001,7 +20444,7 @@
         <v>30</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -19010,10 +20453,10 @@
         <v>1</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="K18" s="2">
         <v>13</v>
@@ -19025,7 +20468,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -19048,7 +20491,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="G19" s="1">
         <v>5</v>
@@ -19060,7 +20503,7 @@
         <v>31</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="K19" s="2">
         <v>14</v>
@@ -19093,7 +20536,7 @@
         <v>30</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>397</v>
+        <v>423</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -19105,7 +20548,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="K20" s="2">
         <v>15</v>
@@ -19138,7 +20581,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>398</v>
+        <v>424</v>
       </c>
       <c r="G21" s="1">
         <v>7</v>
@@ -19147,10 +20590,10 @@
         <v>36</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="K21" s="2">
         <v>16</v>
@@ -19162,7 +20605,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>400</v>
+        <v>426</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -19185,7 +20628,7 @@
         <v>35</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -19197,7 +20640,7 @@
         <v>31</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>402</v>
+        <v>428</v>
       </c>
       <c r="K22" s="2">
         <v>17</v>
@@ -19230,7 +20673,7 @@
         <v>35</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>403</v>
+        <v>429</v>
       </c>
       <c r="G23" s="1">
         <v>10</v>
@@ -19242,7 +20685,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>399</v>
+        <v>425</v>
       </c>
       <c r="K23" s="2">
         <v>18</v>
@@ -19274,7 +20717,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>404</v>
+        <v>430</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -19283,10 +20726,10 @@
         <v>1</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="K24" s="2">
         <v>19</v>
@@ -19298,7 +20741,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>406</v>
+        <v>432</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -19320,7 +20763,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>407</v>
+        <v>433</v>
       </c>
       <c r="G25" s="1">
         <v>5</v>
@@ -19332,7 +20775,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>408</v>
+        <v>434</v>
       </c>
       <c r="K25" s="2">
         <v>20</v>
@@ -19364,7 +20807,7 @@
         <v>40</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>409</v>
+        <v>435</v>
       </c>
       <c r="G26" s="1">
         <v>7</v>
@@ -19376,7 +20819,7 @@
         <v>27</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>405</v>
+        <v>431</v>
       </c>
       <c r="K26" s="2">
         <v>21</v>
@@ -19409,7 +20852,7 @@
         <v>45</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>410</v>
+        <v>436</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -19418,10 +20861,10 @@
         <v>1</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="K27" s="2">
         <v>22</v>
@@ -19433,7 +20876,7 @@
         <v>1</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>412</v>
+        <v>438</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -19456,7 +20899,7 @@
         <v>45</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>413</v>
+        <v>439</v>
       </c>
       <c r="G28" s="1">
         <v>3</v>
@@ -19468,7 +20911,7 @@
         <v>31</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>414</v>
+        <v>440</v>
       </c>
       <c r="K28" s="2">
         <v>23</v>
@@ -19501,7 +20944,7 @@
         <v>45</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>415</v>
+        <v>441</v>
       </c>
       <c r="G29" s="1">
         <v>7</v>
@@ -19513,7 +20956,7 @@
         <v>27</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>411</v>
+        <v>437</v>
       </c>
       <c r="K29" s="2">
         <v>24</v>
@@ -19546,7 +20989,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="G30" s="1">
         <v>4</v>
@@ -19558,7 +21001,7 @@
         <v>31</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>417</v>
+        <v>443</v>
       </c>
       <c r="K30" s="2">
         <v>25</v>
@@ -19570,7 +21013,7 @@
         <v>1</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>418</v>
+        <v>444</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -19593,7 +21036,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="G31" s="1">
         <v>5</v>
@@ -19602,10 +21045,10 @@
         <v>34</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="K31" s="2">
         <v>26</v>
@@ -19638,7 +21081,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="G32" s="2">
         <v>2</v>
@@ -19650,7 +21093,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>420</v>
+        <v>446</v>
       </c>
       <c r="K32" s="2">
         <v>27</v>
@@ -19683,7 +21126,7 @@
         <v>55</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>422</v>
+        <v>448</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -19695,7 +21138,7 @@
         <v>31</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>423</v>
+        <v>449</v>
       </c>
       <c r="K33" s="2">
         <v>28</v>
@@ -19707,7 +21150,7 @@
         <v>1</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>424</v>
+        <v>450</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -19730,7 +21173,7 @@
         <v>55</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>425</v>
+        <v>451</v>
       </c>
       <c r="G34" s="1">
         <v>3</v>
@@ -19739,10 +21182,10 @@
         <v>3</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="K34" s="2">
         <v>29</v>
@@ -19775,7 +21218,7 @@
         <v>55</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>427</v>
+        <v>453</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -19787,7 +21230,7 @@
         <v>27</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="K35" s="2">
         <v>30</v>
@@ -19818,7 +21261,7 @@
         <v>60</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>428</v>
+        <v>454</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -19830,7 +21273,7 @@
         <v>31</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>429</v>
+        <v>455</v>
       </c>
       <c r="K36" s="2">
         <v>31</v>
@@ -19861,7 +21304,7 @@
         <v>60</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="G37" s="1">
         <v>4</v>
@@ -19870,10 +21313,10 @@
         <v>4</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="K37" s="2">
         <v>32</v>
@@ -19906,7 +21349,7 @@
         <v>60</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>432</v>
+        <v>458</v>
       </c>
       <c r="G38" s="1">
         <v>5</v>
@@ -19918,7 +21361,7 @@
         <v>27</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="K38" s="2">
         <v>33</v>
@@ -19951,7 +21394,7 @@
         <v>65</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="G39" s="2">
         <v>2</v>
@@ -19963,7 +21406,7 @@
         <v>31</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>434</v>
+        <v>460</v>
       </c>
       <c r="K39" s="2">
         <v>34</v>
@@ -19996,7 +21439,7 @@
         <v>65</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="G40" s="1">
         <v>7</v>
@@ -20005,10 +21448,10 @@
         <v>36</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>369</v>
+        <v>395</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="K40" s="2">
         <v>35</v>
@@ -20041,7 +21484,7 @@
         <v>65</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>437</v>
+        <v>463</v>
       </c>
       <c r="G41" s="1">
         <v>10</v>
@@ -20053,7 +21496,7 @@
         <v>27</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>436</v>
+        <v>462</v>
       </c>
       <c r="K41" s="2">
         <v>36</v>
@@ -20074,10 +21517,10 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C42" s="2">
         <v>211037</v>
@@ -20089,7 +21532,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>438</v>
+        <v>464</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -20105,7 +21548,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2" t="s">
-        <v>439</v>
+        <v>465</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -20116,10 +21559,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2">
         <v>211038</v>
@@ -20131,7 +21574,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -20156,10 +21599,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C44" s="2">
         <v>211039</v>
@@ -20171,7 +21614,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>441</v>
+        <v>467</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -20196,10 +21639,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C45" s="2">
         <v>211040</v>
@@ -20211,7 +21654,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>442</v>
+        <v>468</v>
       </c>
       <c r="G45" s="1">
         <v>3</v>
@@ -20227,7 +21670,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>443</v>
+        <v>469</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -20238,10 +21681,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C46" s="2">
         <v>211041</v>
@@ -20253,7 +21696,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>444</v>
+        <v>470</v>
       </c>
       <c r="G46" s="1">
         <v>5</v>
@@ -20278,10 +21721,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>360</v>
+        <v>386</v>
       </c>
       <c r="C47" s="2">
         <v>211042</v>
@@ -20293,7 +21736,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>445</v>
+        <v>471</v>
       </c>
       <c r="G47" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -18294,7 +18294,7 @@
         <v>240001</v>
       </c>
       <c r="D6" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="1">
         <v>61</v>
@@ -18341,7 +18341,7 @@
         <v>240002</v>
       </c>
       <c r="D7" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="1">
         <v>61</v>
@@ -18388,7 +18388,7 @@
         <v>240003</v>
       </c>
       <c r="D8" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" s="1">
         <v>61</v>
@@ -18435,7 +18435,7 @@
         <v>240004</v>
       </c>
       <c r="D9" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" s="1">
         <v>61</v>
@@ -18482,7 +18482,7 @@
         <v>240005</v>
       </c>
       <c r="D10" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="1">
         <v>61</v>
@@ -18529,7 +18529,7 @@
         <v>240006</v>
       </c>
       <c r="D11" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" s="1">
         <v>61</v>
@@ -18576,7 +18576,7 @@
         <v>240007</v>
       </c>
       <c r="D12" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" s="1">
         <v>61</v>
@@ -18623,7 +18623,7 @@
         <v>240008</v>
       </c>
       <c r="D13" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" s="1">
         <v>61</v>
@@ -18670,7 +18670,7 @@
         <v>250001</v>
       </c>
       <c r="D14" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" s="1">
         <v>61</v>
@@ -18717,7 +18717,7 @@
         <v>250002</v>
       </c>
       <c r="D15" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1">
         <v>61</v>
@@ -18764,7 +18764,7 @@
         <v>250003</v>
       </c>
       <c r="D16" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="1">
         <v>61</v>
@@ -18811,7 +18811,7 @@
         <v>250004</v>
       </c>
       <c r="D17" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="1">
         <v>61</v>
@@ -18858,7 +18858,7 @@
         <v>250005</v>
       </c>
       <c r="D18" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="1">
         <v>61</v>
@@ -18905,7 +18905,7 @@
         <v>250006</v>
       </c>
       <c r="D19" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" s="1">
         <v>61</v>
@@ -18952,7 +18952,7 @@
         <v>250007</v>
       </c>
       <c r="D20" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="1">
         <v>61</v>
@@ -18999,7 +18999,7 @@
         <v>250008</v>
       </c>
       <c r="D21" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" s="1">
         <v>61</v>
@@ -19046,7 +19046,7 @@
         <v>260001</v>
       </c>
       <c r="D22" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" s="1">
         <v>61</v>
@@ -19093,7 +19093,7 @@
         <v>260002</v>
       </c>
       <c r="D23" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" s="1">
         <v>61</v>
@@ -19140,7 +19140,7 @@
         <v>260003</v>
       </c>
       <c r="D24" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" s="1">
         <v>61</v>
@@ -19187,7 +19187,7 @@
         <v>260004</v>
       </c>
       <c r="D25" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="1">
         <v>61</v>
@@ -19234,7 +19234,7 @@
         <v>260005</v>
       </c>
       <c r="D26" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" s="1">
         <v>61</v>
@@ -19281,7 +19281,7 @@
         <v>260006</v>
       </c>
       <c r="D27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="1">
         <v>61</v>
@@ -19328,7 +19328,7 @@
         <v>260007</v>
       </c>
       <c r="D28" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="1">
         <v>61</v>
@@ -19375,7 +19375,7 @@
         <v>260008</v>
       </c>
       <c r="D29" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" s="1">
         <v>61</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -2015,12 +2015,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -18132,7 +18132,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q29"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="14"/>
   <cols>
     <col min="5" max="5" width="14.1666666666667" customWidth="1"/>
@@ -19416,6 +19416,12 @@
       <c r="Q29" s="9">
         <v>0</v>
       </c>
+    </row>
+    <row r="36" spans="5:10">
+      <c r="E36" s="1"/>
+    </row>
+    <row r="37" spans="5:10">
+      <c r="J37" s="1"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -421,7 +421,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="473">
   <si>
     <t>_id</t>
   </si>
@@ -1488,7 +1488,7 @@
     <t>天龙战刃</t>
   </si>
   <si>
-    <t>60000,40</t>
+    <t>50000,40</t>
   </si>
   <si>
     <t>天龙战甲</t>
@@ -1497,10 +1497,13 @@
     <t>天龙战链</t>
   </si>
   <si>
-    <t>30000,20</t>
+    <t>25000,20</t>
   </si>
   <si>
     <t>天龙战盔</t>
+  </si>
+  <si>
+    <t>500000,40</t>
   </si>
   <si>
     <t>天龙战镯</t>
@@ -18453,7 +18456,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K9" s="9">
         <v>1500</v>
@@ -18488,7 +18491,7 @@
         <v>61</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="G10" s="1">
         <v>5</v>
@@ -18500,7 +18503,7 @@
         <v>31</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K10" s="9">
         <v>1500</v>
@@ -18535,7 +18538,7 @@
         <v>61</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="G11" s="1">
         <v>7</v>
@@ -18582,7 +18585,7 @@
         <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="G12" s="1">
         <v>9</v>
@@ -18629,7 +18632,7 @@
         <v>61</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G13" s="1">
         <v>10</v>
@@ -18641,7 +18644,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K13" s="9">
         <v>1500</v>
@@ -18676,7 +18679,7 @@
         <v>61</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G14" s="1">
         <v>1</v>
@@ -18723,7 +18726,7 @@
         <v>61</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="G15" s="1">
         <v>2</v>
@@ -18770,7 +18773,7 @@
         <v>61</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -18817,7 +18820,7 @@
         <v>61</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="G17" s="1">
         <v>4</v>
@@ -18829,7 +18832,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K17" s="9">
         <v>1500</v>
@@ -18864,7 +18867,7 @@
         <v>61</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="G18" s="1">
         <v>5</v>
@@ -18876,7 +18879,7 @@
         <v>31</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K18" s="9">
         <v>1500</v>
@@ -18911,7 +18914,7 @@
         <v>61</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G19" s="1">
         <v>7</v>
@@ -18958,7 +18961,7 @@
         <v>61</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -19005,7 +19008,7 @@
         <v>61</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="G21" s="1">
         <v>10</v>
@@ -19017,7 +19020,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K21" s="9">
         <v>1500</v>
@@ -19052,7 +19055,7 @@
         <v>61</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G22" s="1">
         <v>1</v>
@@ -19099,7 +19102,7 @@
         <v>61</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="G23" s="1">
         <v>2</v>
@@ -19146,7 +19149,7 @@
         <v>61</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="G24" s="1">
         <v>3</v>
@@ -19193,7 +19196,7 @@
         <v>61</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G25" s="1">
         <v>4</v>
@@ -19205,7 +19208,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K25" s="9">
         <v>1500</v>
@@ -19240,7 +19243,7 @@
         <v>61</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="G26" s="1">
         <v>5</v>
@@ -19252,7 +19255,7 @@
         <v>31</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K26" s="9">
         <v>1500</v>
@@ -19287,7 +19290,7 @@
         <v>61</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="G27" s="1">
         <v>7</v>
@@ -19334,7 +19337,7 @@
         <v>61</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="G28" s="1">
         <v>9</v>
@@ -19381,7 +19384,7 @@
         <v>61</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="G29" s="1">
         <v>10</v>
@@ -19393,7 +19396,7 @@
         <v>31</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K29" s="9">
         <v>1500</v>
@@ -19604,7 +19607,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="G6" s="1">
         <v>1</v>
@@ -19613,10 +19616,10 @@
         <v>1</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="K6" s="1">
         <v>1</v>
@@ -19651,7 +19654,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="G7" s="1">
         <v>2</v>
@@ -19660,10 +19663,10 @@
         <v>2</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="K7" s="1">
         <v>1</v>
@@ -19735,7 +19738,7 @@
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -19753,7 +19756,7 @@
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="1:16">
@@ -19784,16 +19787,16 @@
         <v>7</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M3" s="4" t="s">
         <v>9</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="O3" s="7" t="s">
         <v>13</v>
@@ -19830,10 +19833,10 @@
         <v>17</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M4" s="4" t="s">
         <v>9</v>
@@ -19903,7 +19906,7 @@
         <v>10</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="G6" s="1">
         <v>4</v>
@@ -19915,7 +19918,7 @@
         <v>31</v>
       </c>
       <c r="J6" s="17" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="K6" s="2">
         <v>1</v>
@@ -19927,7 +19930,7 @@
         <v>1</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="O6" s="1">
         <v>0</v>
@@ -19949,7 +19952,7 @@
         <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G7" s="1">
         <v>5</v>
@@ -19958,10 +19961,10 @@
         <v>34</v>
       </c>
       <c r="I7" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J7" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K7" s="2">
         <v>2</v>
@@ -19973,7 +19976,7 @@
         <v>1</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="O7" s="1">
         <v>0</v>
@@ -19995,7 +19998,7 @@
         <v>10</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G8" s="2">
         <v>2</v>
@@ -20007,7 +20010,7 @@
         <v>27</v>
       </c>
       <c r="J8" s="17" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="K8" s="2">
         <v>3</v>
@@ -20039,7 +20042,7 @@
         <v>15</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="G9" s="1">
         <v>7</v>
@@ -20051,7 +20054,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="K9" s="2">
         <v>4</v>
@@ -20063,7 +20066,7 @@
         <v>1</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="O9" s="1">
         <v>0</v>
@@ -20085,7 +20088,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="G10" s="1">
         <v>3</v>
@@ -20094,10 +20097,10 @@
         <v>3</v>
       </c>
       <c r="I10" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J10" s="17" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K10" s="2">
         <v>5</v>
@@ -20109,7 +20112,7 @@
         <v>1</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="O10" s="1">
         <v>0</v>
@@ -20131,7 +20134,7 @@
         <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="G11" s="1">
         <v>9</v>
@@ -20143,7 +20146,7 @@
         <v>27</v>
       </c>
       <c r="J11" s="17" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="K11" s="2">
         <v>6</v>
@@ -20176,7 +20179,7 @@
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -20185,10 +20188,10 @@
         <v>1</v>
       </c>
       <c r="I12" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J12" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K12" s="2">
         <v>7</v>
@@ -20200,7 +20203,7 @@
         <v>1</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="O12" s="1">
         <v>0</v>
@@ -20223,7 +20226,7 @@
         <v>20</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="G13" s="1">
         <v>4</v>
@@ -20235,7 +20238,7 @@
         <v>31</v>
       </c>
       <c r="J13" s="17" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="K13" s="2">
         <v>8</v>
@@ -20268,7 +20271,7 @@
         <v>20</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G14" s="1">
         <v>10</v>
@@ -20280,7 +20283,7 @@
         <v>27</v>
       </c>
       <c r="J14" s="17" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="K14" s="2">
         <v>9</v>
@@ -20313,7 +20316,7 @@
         <v>25</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G15" s="1">
         <v>4</v>
@@ -20322,10 +20325,10 @@
         <v>4</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J15" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K15" s="2">
         <v>10</v>
@@ -20337,7 +20340,7 @@
         <v>1</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="O15" s="1">
         <v>0</v>
@@ -20360,7 +20363,7 @@
         <v>25</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G16" s="1">
         <v>3</v>
@@ -20372,7 +20375,7 @@
         <v>27</v>
       </c>
       <c r="J16" s="18" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="K16" s="2">
         <v>11</v>
@@ -20405,7 +20408,7 @@
         <v>25</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="G17" s="1">
         <v>7</v>
@@ -20417,7 +20420,7 @@
         <v>31</v>
       </c>
       <c r="J17" s="17" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="K17" s="2">
         <v>12</v>
@@ -20450,7 +20453,7 @@
         <v>30</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G18" s="2">
         <v>1</v>
@@ -20459,10 +20462,10 @@
         <v>1</v>
       </c>
       <c r="I18" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J18" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K18" s="2">
         <v>13</v>
@@ -20474,7 +20477,7 @@
         <v>1</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="O18" s="1">
         <v>0</v>
@@ -20497,7 +20500,7 @@
         <v>30</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="G19" s="1">
         <v>5</v>
@@ -20509,7 +20512,7 @@
         <v>31</v>
       </c>
       <c r="J19" s="17" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="K19" s="2">
         <v>14</v>
@@ -20542,7 +20545,7 @@
         <v>30</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G20" s="1">
         <v>9</v>
@@ -20554,7 +20557,7 @@
         <v>27</v>
       </c>
       <c r="J20" s="17" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="K20" s="2">
         <v>15</v>
@@ -20587,7 +20590,7 @@
         <v>35</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="G21" s="1">
         <v>7</v>
@@ -20596,10 +20599,10 @@
         <v>36</v>
       </c>
       <c r="I21" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J21" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K21" s="2">
         <v>16</v>
@@ -20611,7 +20614,7 @@
         <v>1</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="O21" s="1">
         <v>0</v>
@@ -20634,7 +20637,7 @@
         <v>35</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G22" s="2">
         <v>2</v>
@@ -20646,7 +20649,7 @@
         <v>31</v>
       </c>
       <c r="J22" s="17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="K22" s="2">
         <v>17</v>
@@ -20679,7 +20682,7 @@
         <v>35</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="G23" s="1">
         <v>10</v>
@@ -20691,7 +20694,7 @@
         <v>27</v>
       </c>
       <c r="J23" s="17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="K23" s="2">
         <v>18</v>
@@ -20723,7 +20726,7 @@
         <v>40</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="G24" s="1">
         <v>1</v>
@@ -20732,10 +20735,10 @@
         <v>1</v>
       </c>
       <c r="I24" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J24" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K24" s="2">
         <v>19</v>
@@ -20747,7 +20750,7 @@
         <v>1</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O24" s="1">
         <v>0</v>
@@ -20769,7 +20772,7 @@
         <v>40</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="G25" s="1">
         <v>5</v>
@@ -20781,7 +20784,7 @@
         <v>31</v>
       </c>
       <c r="J25" s="17" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="K25" s="2">
         <v>20</v>
@@ -20813,7 +20816,7 @@
         <v>40</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G26" s="1">
         <v>7</v>
@@ -20825,7 +20828,7 @@
         <v>27</v>
       </c>
       <c r="J26" s="17" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="K26" s="2">
         <v>21</v>
@@ -20858,7 +20861,7 @@
         <v>45</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G27" s="1">
         <v>1</v>
@@ -20867,10 +20870,10 @@
         <v>1</v>
       </c>
       <c r="I27" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J27" s="17" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K27" s="2">
         <v>22</v>
@@ -20882,7 +20885,7 @@
         <v>1</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O27" s="1">
         <v>0</v>
@@ -20905,7 +20908,7 @@
         <v>45</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G28" s="1">
         <v>3</v>
@@ -20917,7 +20920,7 @@
         <v>31</v>
       </c>
       <c r="J28" s="17" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="K28" s="2">
         <v>23</v>
@@ -20950,7 +20953,7 @@
         <v>45</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G29" s="1">
         <v>7</v>
@@ -20962,7 +20965,7 @@
         <v>27</v>
       </c>
       <c r="J29" s="17" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K29" s="2">
         <v>24</v>
@@ -20995,7 +20998,7 @@
         <v>50</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="G30" s="1">
         <v>4</v>
@@ -21007,7 +21010,7 @@
         <v>31</v>
       </c>
       <c r="J30" s="17" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="K30" s="2">
         <v>25</v>
@@ -21019,7 +21022,7 @@
         <v>1</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O30" s="1">
         <v>0</v>
@@ -21042,7 +21045,7 @@
         <v>50</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="G31" s="1">
         <v>5</v>
@@ -21051,10 +21054,10 @@
         <v>34</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J31" s="17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K31" s="2">
         <v>26</v>
@@ -21087,7 +21090,7 @@
         <v>50</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="G32" s="2">
         <v>2</v>
@@ -21099,7 +21102,7 @@
         <v>27</v>
       </c>
       <c r="J32" s="17" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="K32" s="2">
         <v>27</v>
@@ -21132,7 +21135,7 @@
         <v>55</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G33" s="1">
         <v>7</v>
@@ -21144,7 +21147,7 @@
         <v>31</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="K33" s="2">
         <v>28</v>
@@ -21156,7 +21159,7 @@
         <v>1</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O33" s="1">
         <v>0</v>
@@ -21179,7 +21182,7 @@
         <v>55</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="G34" s="1">
         <v>3</v>
@@ -21188,10 +21191,10 @@
         <v>3</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J34" s="17" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K34" s="2">
         <v>29</v>
@@ -21224,7 +21227,7 @@
         <v>55</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G35" s="1">
         <v>9</v>
@@ -21236,7 +21239,7 @@
         <v>27</v>
       </c>
       <c r="J35" s="17" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="K35" s="2">
         <v>30</v>
@@ -21267,7 +21270,7 @@
         <v>60</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -21279,7 +21282,7 @@
         <v>31</v>
       </c>
       <c r="J36" s="17" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="K36" s="2">
         <v>31</v>
@@ -21310,7 +21313,7 @@
         <v>60</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="G37" s="1">
         <v>4</v>
@@ -21319,10 +21322,10 @@
         <v>4</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J37" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K37" s="2">
         <v>32</v>
@@ -21355,7 +21358,7 @@
         <v>60</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="G38" s="1">
         <v>5</v>
@@ -21367,7 +21370,7 @@
         <v>27</v>
       </c>
       <c r="J38" s="17" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="K38" s="2">
         <v>33</v>
@@ -21400,7 +21403,7 @@
         <v>65</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="G39" s="2">
         <v>2</v>
@@ -21412,7 +21415,7 @@
         <v>31</v>
       </c>
       <c r="J39" s="17" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="K39" s="2">
         <v>34</v>
@@ -21445,7 +21448,7 @@
         <v>65</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G40" s="1">
         <v>7</v>
@@ -21454,10 +21457,10 @@
         <v>36</v>
       </c>
       <c r="I40" s="17" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J40" s="17" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K40" s="2">
         <v>35</v>
@@ -21490,7 +21493,7 @@
         <v>65</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="G41" s="1">
         <v>10</v>
@@ -21502,7 +21505,7 @@
         <v>27</v>
       </c>
       <c r="J41" s="17" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="K41" s="2">
         <v>36</v>
@@ -21523,10 +21526,10 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A42" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C42" s="2">
         <v>211037</v>
@@ -21538,7 +21541,7 @@
         <v>10</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G42" s="1">
         <v>1</v>
@@ -21554,7 +21557,7 @@
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O42" s="1">
         <v>0</v>
@@ -21565,10 +21568,10 @@
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A43" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C43" s="2">
         <v>211038</v>
@@ -21580,7 +21583,7 @@
         <v>10</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G43" s="1">
         <v>5</v>
@@ -21605,10 +21608,10 @@
     </row>
     <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A44" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C44" s="2">
         <v>211039</v>
@@ -21620,7 +21623,7 @@
         <v>10</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G44" s="1">
         <v>7</v>
@@ -21645,10 +21648,10 @@
     </row>
     <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A45" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C45" s="2">
         <v>211040</v>
@@ -21660,7 +21663,7 @@
         <v>10</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G45" s="1">
         <v>3</v>
@@ -21676,7 +21679,7 @@
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O45" s="1">
         <v>0</v>
@@ -21687,10 +21690,10 @@
     </row>
     <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A46" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C46" s="2">
         <v>211041</v>
@@ -21702,7 +21705,7 @@
         <v>10</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G46" s="1">
         <v>5</v>
@@ -21727,10 +21730,10 @@
     </row>
     <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A47" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C47" s="2">
         <v>211042</v>
@@ -21742,7 +21745,7 @@
         <v>10</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G47" s="1">
         <v>7</v>

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="3"/>
+    <workbookView windowHeight="17680" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="0-40" sheetId="7" r:id="rId1"/>
@@ -421,7 +421,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="473">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1472" uniqueCount="484">
   <si>
     <t>_id</t>
   </si>
@@ -1816,6 +1816,39 @@
   </si>
   <si>
     <t>斩杀铁履</t>
+  </si>
+  <si>
+    <t>不灭护面</t>
+  </si>
+  <si>
+    <t>100000,30</t>
+  </si>
+  <si>
+    <t>不灭护手</t>
+  </si>
+  <si>
+    <t>10000,30</t>
+  </si>
+  <si>
+    <t>不灭护袍</t>
+  </si>
+  <si>
+    <t>镇岳铁甲</t>
+  </si>
+  <si>
+    <t>镇岳铁带</t>
+  </si>
+  <si>
+    <t>镇岳铁腿</t>
+  </si>
+  <si>
+    <t>冰霜项链</t>
+  </si>
+  <si>
+    <t>冰霜戒指</t>
+  </si>
+  <si>
+    <t>冰霜银带</t>
   </si>
   <si>
     <t>毒蛇之刺</t>
@@ -19705,7 +19738,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P78"/>
+  <dimension ref="A1:P88"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.125" style="1" customWidth="1"/>
@@ -20175,7 +20208,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="2">
-        <f t="shared" ref="E12:E41" si="0">E9+5</f>
+        <f t="shared" ref="E12:E44" si="0">E9+5</f>
         <v>20</v>
       </c>
       <c r="F12" s="2" t="s">
@@ -21524,41 +21557,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A42" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C42" s="2">
-        <v>211037</v>
+    <row r="42" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A42" s="1"/>
+      <c r="B42" s="1"/>
+      <c r="C42" s="1">
+        <v>201037</v>
       </c>
       <c r="D42" s="2">
         <v>10</v>
       </c>
       <c r="E42" s="2">
-        <v>10</v>
-      </c>
-      <c r="F42" s="2" t="s">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F42" s="1" t="s">
         <v>465</v>
       </c>
       <c r="G42" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H42" s="1">
-        <v>1</v>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="I42" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J42" s="17" t="s">
+        <v>466</v>
+      </c>
       <c r="K42" s="2">
-        <v>10</v>
-      </c>
-      <c r="L42" s="2"/>
-      <c r="M42" s="2"/>
-      <c r="N42" s="2" t="s">
-        <v>466</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="L42" s="2">
+        <v>7</v>
+      </c>
+      <c r="M42" s="2">
+        <v>1</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="1">
         <v>0</v>
       </c>
@@ -21566,23 +21602,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A43" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C43" s="2">
-        <v>211038</v>
+    <row r="43" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A43" s="1"/>
+      <c r="B43" s="1"/>
+      <c r="C43" s="1">
+        <v>201038</v>
       </c>
       <c r="D43" s="2">
         <v>10</v>
       </c>
       <c r="E43" s="2">
-        <v>10</v>
-      </c>
-      <c r="F43" s="2" t="s">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>467</v>
       </c>
       <c r="G43" s="1">
@@ -21591,13 +21624,21 @@
       <c r="H43" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
+      <c r="I43" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="J43" s="17" t="s">
+        <v>468</v>
+      </c>
       <c r="K43" s="2">
-        <v>10</v>
-      </c>
-      <c r="L43" s="2"/>
-      <c r="M43" s="2"/>
+        <v>38</v>
+      </c>
+      <c r="L43" s="2">
+        <v>7</v>
+      </c>
+      <c r="M43" s="2">
+        <v>1</v>
+      </c>
       <c r="N43" s="2"/>
       <c r="O43" s="1">
         <v>0</v>
@@ -21606,38 +21647,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A44" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C44" s="2">
-        <v>211039</v>
+    <row r="44" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A44" s="1"/>
+      <c r="B44" s="1"/>
+      <c r="C44" s="1">
+        <v>201039</v>
       </c>
       <c r="D44" s="2">
         <v>10</v>
       </c>
       <c r="E44" s="2">
-        <v>10</v>
-      </c>
-      <c r="F44" s="2" t="s">
+        <f t="shared" si="0"/>
+        <v>70</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G44" s="2">
+        <v>2</v>
+      </c>
+      <c r="H44" s="2">
+        <v>2</v>
+      </c>
+      <c r="I44" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J44" s="17" t="s">
         <v>468</v>
       </c>
-      <c r="G44" s="1">
+      <c r="K44" s="2">
+        <v>39</v>
+      </c>
+      <c r="L44" s="2">
         <v>7</v>
       </c>
-      <c r="H44" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2">
-        <v>10</v>
-      </c>
-      <c r="L44" s="2"/>
-      <c r="M44" s="2"/>
+      <c r="M44" s="2">
+        <v>1</v>
+      </c>
       <c r="N44" s="2"/>
       <c r="O44" s="1">
         <v>0</v>
@@ -21646,41 +21692,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A45" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C45" s="2">
-        <v>211040</v>
+    <row r="45" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1">
+        <v>201040</v>
       </c>
       <c r="D45" s="2">
         <v>10</v>
       </c>
       <c r="E45" s="2">
-        <v>10</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="G45" s="1">
-        <v>3</v>
-      </c>
-      <c r="H45" s="1">
-        <v>3</v>
-      </c>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
+        <f t="shared" ref="E45:E50" si="1">E42+5</f>
+        <v>75</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G45" s="2">
+        <v>2</v>
+      </c>
+      <c r="H45" s="2">
+        <v>2</v>
+      </c>
+      <c r="I45" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J45" s="17" t="s">
+        <v>466</v>
+      </c>
       <c r="K45" s="2">
-        <v>3</v>
-      </c>
-      <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2" t="s">
-        <v>470</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="L45" s="2">
+        <v>7</v>
+      </c>
+      <c r="M45" s="2">
+        <v>1</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="1">
         <v>0</v>
       </c>
@@ -21688,38 +21737,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A46" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C46" s="2">
-        <v>211041</v>
+    <row r="46" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A46" s="1"/>
+      <c r="B46" s="1"/>
+      <c r="C46" s="1">
+        <v>201041</v>
       </c>
       <c r="D46" s="2">
         <v>10</v>
       </c>
       <c r="E46" s="2">
-        <v>10</v>
-      </c>
-      <c r="F46" s="2" t="s">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="F46" s="1" t="s">
         <v>471</v>
       </c>
       <c r="G46" s="1">
-        <v>5</v>
-      </c>
-      <c r="H46" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="H46" s="1">
+        <v>9</v>
+      </c>
+      <c r="I46" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="J46" s="17" t="s">
+        <v>468</v>
+      </c>
       <c r="K46" s="2">
-        <v>3</v>
-      </c>
-      <c r="L46" s="2"/>
-      <c r="M46" s="2"/>
+        <v>41</v>
+      </c>
+      <c r="L46" s="2">
+        <v>7</v>
+      </c>
+      <c r="M46" s="2">
+        <v>1</v>
+      </c>
       <c r="N46" s="2"/>
       <c r="O46" s="1">
         <v>0</v>
@@ -21728,38 +21782,43 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" s="1" customFormat="1" customHeight="1" spans="1:16">
-      <c r="A47" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="C47" s="2">
-        <v>211042</v>
+    <row r="47" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A47" s="1"/>
+      <c r="B47" s="1"/>
+      <c r="C47" s="1">
+        <v>201042</v>
       </c>
       <c r="D47" s="2">
         <v>10</v>
       </c>
       <c r="E47" s="2">
+        <f t="shared" si="1"/>
+        <v>75</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="G47" s="1">
         <v>10</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="G47" s="1">
+      <c r="H47" s="1">
+        <v>10</v>
+      </c>
+      <c r="I47" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J47" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="K47" s="2">
+        <v>42</v>
+      </c>
+      <c r="L47" s="2">
         <v>7</v>
       </c>
-      <c r="H47" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="I47" s="2"/>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2">
-        <v>3</v>
-      </c>
-      <c r="L47" s="2"/>
-      <c r="M47" s="2"/>
+      <c r="M47" s="2">
+        <v>1</v>
+      </c>
       <c r="N47" s="2"/>
       <c r="O47" s="1">
         <v>0</v>
@@ -21768,13 +21827,410 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" customHeight="1" spans="15:16">
-      <c r="O77"/>
-      <c r="P77"/>
-    </row>
-    <row r="78" customHeight="1" spans="15:16">
-      <c r="O78"/>
-      <c r="P78"/>
+    <row r="48" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1">
+        <v>201043</v>
+      </c>
+      <c r="D48" s="2">
+        <v>10</v>
+      </c>
+      <c r="E48" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="G48" s="2">
+        <v>2</v>
+      </c>
+      <c r="H48" s="2">
+        <v>2</v>
+      </c>
+      <c r="I48" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J48" s="17" t="s">
+        <v>466</v>
+      </c>
+      <c r="K48" s="2">
+        <v>43</v>
+      </c>
+      <c r="L48" s="2">
+        <v>7</v>
+      </c>
+      <c r="M48" s="2">
+        <v>1</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="1">
+        <v>0</v>
+      </c>
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A49" s="1"/>
+      <c r="B49" s="1"/>
+      <c r="C49" s="1">
+        <v>201044</v>
+      </c>
+      <c r="D49" s="2">
+        <v>10</v>
+      </c>
+      <c r="E49" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G49" s="1">
+        <v>7</v>
+      </c>
+      <c r="H49" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I49" s="17" t="s">
+        <v>396</v>
+      </c>
+      <c r="J49" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="K49" s="2">
+        <v>44</v>
+      </c>
+      <c r="L49" s="2">
+        <v>7</v>
+      </c>
+      <c r="M49" s="2">
+        <v>1</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="1">
+        <v>0</v>
+      </c>
+      <c r="P49" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A50" s="1"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="1">
+        <v>201045</v>
+      </c>
+      <c r="D50" s="2">
+        <v>10</v>
+      </c>
+      <c r="E50" s="2">
+        <f t="shared" si="1"/>
+        <v>80</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="G50" s="1">
+        <v>9</v>
+      </c>
+      <c r="H50" s="1">
+        <v>9</v>
+      </c>
+      <c r="I50" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="J50" s="17" t="s">
+        <v>468</v>
+      </c>
+      <c r="K50" s="2">
+        <v>45</v>
+      </c>
+      <c r="L50" s="2">
+        <v>7</v>
+      </c>
+      <c r="M50" s="2">
+        <v>1</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="1">
+        <v>0</v>
+      </c>
+      <c r="P50" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A51" s="1"/>
+      <c r="B51" s="1"/>
+      <c r="C51" s="1"/>
+      <c r="D51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A52" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C52" s="2">
+        <v>211037</v>
+      </c>
+      <c r="D52" s="2">
+        <v>10</v>
+      </c>
+      <c r="E52" s="2">
+        <v>10</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="G52" s="1">
+        <v>1</v>
+      </c>
+      <c r="H52" s="1">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2">
+        <v>10</v>
+      </c>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="O52" s="1">
+        <v>0</v>
+      </c>
+      <c r="P52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A53" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C53" s="2">
+        <v>211038</v>
+      </c>
+      <c r="D53" s="2">
+        <v>10</v>
+      </c>
+      <c r="E53" s="2">
+        <v>10</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="G53" s="1">
+        <v>5</v>
+      </c>
+      <c r="H53" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2">
+        <v>10</v>
+      </c>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="1">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A54" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C54" s="2">
+        <v>211039</v>
+      </c>
+      <c r="D54" s="2">
+        <v>10</v>
+      </c>
+      <c r="E54" s="2">
+        <v>10</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="G54" s="1">
+        <v>7</v>
+      </c>
+      <c r="H54" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2">
+        <v>10</v>
+      </c>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="1">
+        <v>0</v>
+      </c>
+      <c r="P54" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A55" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C55" s="2">
+        <v>211040</v>
+      </c>
+      <c r="D55" s="2">
+        <v>10</v>
+      </c>
+      <c r="E55" s="2">
+        <v>10</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="G55" s="1">
+        <v>3</v>
+      </c>
+      <c r="H55" s="1">
+        <v>3</v>
+      </c>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2">
+        <v>3</v>
+      </c>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="O55" s="1">
+        <v>0</v>
+      </c>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A56" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C56" s="2">
+        <v>211041</v>
+      </c>
+      <c r="D56" s="2">
+        <v>10</v>
+      </c>
+      <c r="E56" s="2">
+        <v>10</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="G56" s="1">
+        <v>5</v>
+      </c>
+      <c r="H56" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2">
+        <v>3</v>
+      </c>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="1">
+        <v>0</v>
+      </c>
+      <c r="P56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="1:16">
+      <c r="A57" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C57" s="2">
+        <v>211042</v>
+      </c>
+      <c r="D57" s="2">
+        <v>10</v>
+      </c>
+      <c r="E57" s="2">
+        <v>10</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="G57" s="1">
+        <v>7</v>
+      </c>
+      <c r="H57" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2">
+        <v>3</v>
+      </c>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="1">
+        <v>0</v>
+      </c>
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" customHeight="1" spans="15:16">
+      <c r="O87"/>
+      <c r="P87"/>
+    </row>
+    <row r="88" customHeight="1" spans="15:16">
+      <c r="O88"/>
+      <c r="P88"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/EquipConfig.xlsx
+++ b/Excel/EquipConfig.xlsx
@@ -2051,12 +2051,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -19960,7 +19960,7 @@
         <v>7</v>
       </c>
       <c r="M6" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>394</v>
@@ -20006,7 +20006,7 @@
         <v>7</v>
       </c>
       <c r="M7" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N7" s="2" t="s">
         <v>398</v>
@@ -20052,7 +20052,7 @@
         <v>7</v>
       </c>
       <c r="M8" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="1">
@@ -20096,7 +20096,7 @@
         <v>7</v>
       </c>
       <c r="M9" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>402</v>
@@ -20142,7 +20142,7 @@
         <v>7</v>
       </c>
       <c r="M10" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>405</v>
@@ -20188,7 +20188,7 @@
         <v>7</v>
       </c>
       <c r="M11" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="1">
@@ -20233,7 +20233,7 @@
         <v>7</v>
       </c>
       <c r="M12" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N12" s="2" t="s">
         <v>409</v>
@@ -20280,7 +20280,7 @@
         <v>7</v>
       </c>
       <c r="M13" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N13" s="8"/>
       <c r="O13" s="1">
@@ -20325,7 +20325,7 @@
         <v>7</v>
       </c>
       <c r="M14" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N14" s="8"/>
       <c r="O14" s="1">
@@ -20370,7 +20370,7 @@
         <v>7</v>
       </c>
       <c r="M15" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>415</v>
@@ -20417,7 +20417,7 @@
         <v>7</v>
       </c>
       <c r="M16" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="1">
@@ -20462,7 +20462,7 @@
         <v>7</v>
       </c>
       <c r="M17" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="1">
@@ -20507,7 +20507,7 @@
         <v>7</v>
       </c>
       <c r="M18" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>421</v>
@@ -20554,7 +20554,7 @@
         <v>7</v>
       </c>
       <c r="M19" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="1">
@@ -20599,7 +20599,7 @@
         <v>7</v>
       </c>
       <c r="M20" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="1">
@@ -20644,7 +20644,7 @@
         <v>7</v>
       </c>
       <c r="M21" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N21" s="2" t="s">
         <v>427</v>
@@ -20691,7 +20691,7 @@
         <v>7</v>
       </c>
       <c r="M22" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="1">
@@ -20736,7 +20736,7 @@
         <v>7</v>
       </c>
       <c r="M23" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="1">
@@ -20780,7 +20780,7 @@
         <v>7</v>
       </c>
       <c r="M24" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>433</v>
@@ -20826,7 +20826,7 @@
         <v>7</v>
       </c>
       <c r="M25" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="1">
@@ -20870,7 +20870,7 @@
         <v>7</v>
       </c>
       <c r="M26" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="1">
@@ -20915,7 +20915,7 @@
         <v>7</v>
       </c>
       <c r="M27" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>439</v>
@@ -20962,7 +20962,7 @@
         <v>7</v>
       </c>
       <c r="M28" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="1">
@@ -21007,7 +21007,7 @@
         <v>7</v>
       </c>
       <c r="M29" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="1">
@@ -21052,7 +21052,7 @@
         <v>7</v>
       </c>
       <c r="M30" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N30" s="2" t="s">
         <v>445</v>
@@ -21099,7 +21099,7 @@
         <v>7</v>
       </c>
       <c r="M31" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="1">
@@ -21144,7 +21144,7 @@
         <v>7</v>
       </c>
       <c r="M32" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="1">
@@ -21189,7 +21189,7 @@
         <v>7</v>
       </c>
       <c r="M33" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>451</v>
@@ -21236,7 +21236,7 @@
         <v>7</v>
       </c>
       <c r="M34" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="1">
@@ -21281,7 +21281,7 @@
         <v>7</v>
       </c>
       <c r="M35" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="1">
@@ -21324,7 +21324,7 @@
         <v>7</v>
       </c>
       <c r="M36" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="1">
@@ -21367,7 +21367,7 @@
         <v>7</v>
       </c>
       <c r="M37" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="1">
@@ -21412,7 +21412,7 @@
         <v>7</v>
       </c>
       <c r="M38" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="1">
@@ -21457,7 +21457,7 @@
         <v>7</v>
       </c>
       <c r="M39" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="1">
@@ -21502,7 +21502,7 @@
         <v>7</v>
       </c>
       <c r="M40" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="1">
@@ -21547,7 +21547,7 @@
         <v>7</v>
       </c>
       <c r="M41" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="1">
@@ -21592,7 +21592,7 @@
         <v>7</v>
       </c>
       <c r="M42" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="1">
@@ -21637,7 +21637,7 @@
         <v>7</v>
       </c>
       <c r="M43" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="1">
@@ -21682,7 +21682,7 @@
         <v>7</v>
       </c>
       <c r="M44" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="1">
@@ -21727,7 +21727,7 @@
         <v>7</v>
       </c>
       <c r="M45" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="1">
@@ -21772,7 +21772,7 @@
         <v>7</v>
       </c>
       <c r="M46" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="1">
@@ -21817,7 +21817,7 @@
         <v>7</v>
       </c>
       <c r="M47" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="1">
@@ -21862,7 +21862,7 @@
         <v>7</v>
       </c>
       <c r="M48" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="1">
@@ -21907,7 +21907,7 @@
         <v>7</v>
       </c>
       <c r="M49" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="1">
@@ -21952,7 +21952,7 @@
         <v>7</v>
       </c>
       <c r="M50" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="1">
